--- a/templates/Template_9_Room_Profiles.xlsx
+++ b/templates/Template_9_Room_Profiles.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,12 +33,16 @@
     </font>
     <font>
       <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <i val="1"/>
-      <color rgb="00926B18"/>
+      <color rgb="00999999"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -49,12 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="001B4965"/>
         <bgColor rgb="001B4965"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,12 +82,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -455,24 +454,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="24" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
@@ -561,12 +560,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RM_D101</t>
+          <t>RM_J322</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>D-101</t>
+          <t>J-322</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -576,28 +575,28 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>D-Wing</t>
+          <t>J-Wing</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Classroom</t>
+          <t>Art Room</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -610,9 +609,9 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -622,29 +621,25 @@
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Smith, Jane</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>D-102,D-103</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>RM_S231</t>
+          <t>RM_Audit.</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>S-231</t>
+          <t>Audit.</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -654,28 +649,28 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>S-Wing</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Classroom</t>
+          <t>Auditorium</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -688,9 +683,9 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -700,61 +695,61 @@
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>S-232,S-233</t>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RM_SCI1</t>
+          <t>RM_Band</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>I-114</t>
+          <t>Band</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Science</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>I-Wing</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Lab</t>
+          <t>Band Room</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -762,9 +757,9 @@
           <t>N</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -774,85 +769,3549 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>Martino, Brianna</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>I-115,I-117</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>RM_GYM</t>
+          <t>RM_D101</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Gym</t>
+          <t>D-101</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Athletic</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr"/>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>RM_D102</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>D-102</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>RM_D103</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>D-103</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>RM_D104</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>D-104</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>RM_D105</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>D-105</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>RM_D106</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>D-106</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>RM_D107</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>D-107</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>RM_D108</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>D-108</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>RM_D109</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>D-109</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>RM_D110</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>D-110</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>RM_D201</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>D-201</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>RM_D202</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>D-202</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>RM_D203</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>D-203</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>RM_D204</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>D-204</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>McManus, Brianna</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>RM_D205</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>D-205</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>RM_D210</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>D-210</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>RM_I011</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>I-011</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>I-Wing</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>RM_I012</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>I-012</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>I-Wing</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>Winters, Jack</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>RM_I111</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>I-111</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>I-Wing</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>Park, Sam</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>RM_I113</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>I-113</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>I-Wing</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>RM_I114</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>I-114</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>I-Wing</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>RM_I115</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>I-115</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>I-Wing</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>RM_I116</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>I-116</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>I-Wing</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>Fisk, Mary Pat</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>RM_I117</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>I-117</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>I-Wing</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>RM_I118</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>I-118</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>I-Wing</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>New ENGLISH Teacher ELENA (TBD)</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>RM_I119</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>I-119</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>I-Wing</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>RM_J020</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>J-020</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>J-Wing</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>RM_J221</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>J-221</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>J-Wing</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>RM_J320</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>J-320</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>J-Wing</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>RM_J321</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>J-321</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>J-Wing</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>RM_J323</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>J-323</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>J-Wing</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>RM_S231</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>S-231</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>S-Wing</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr"/>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>RM_S232</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>S-232</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>S-Wing</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>RM_S233</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>S-233</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>S-Wing</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>Zawacki, Richard</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>RM_S234</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>S-234</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>S-Wing</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>RM_S235</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>S-235</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>S-Wing</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>RM_S236</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>S-236</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>S-Wing</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>Zawiski, Brian</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>RM_S237</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>S-237</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>S-Wing</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>Muscat, Nicole</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>RM_S238</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>S-238</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>S-Wing</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>Corcoran, Kevin</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>RM_S338</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>S-338</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>S-Wing</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>McConnell, George</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>RM_J222</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>J-222</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>J-Wing</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>Laracy, John</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>RM_J223</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>J-223</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>J-Wing</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Lab</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>Calidas, Riddhi</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>RM_Gymnasium</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>Gymnasium</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>A,B,C,D,E,F,G</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Gymnasium</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>RM_D206</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>D-206</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>D-Wing</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Lecture Hall</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>RM_Center</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Center</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Success Center</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>RM_TBD</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>New ENGLISH Teacher (TBD)</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>RM_Unassigned</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Main</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>Unassigned</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/templates/Template_9_Room_Profiles.xlsx
+++ b/templates/Template_9_Room_Profiles.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1404,11 +1404,11 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>J-322</t>
+          <t>J-323</t>
         </is>
       </c>
       <c r="B38" s="3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
@@ -1429,11 +1429,11 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>J-323</t>
+          <t>S-231</t>
         </is>
       </c>
       <c r="B39" s="3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
@@ -1454,11 +1454,11 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>S-231</t>
+          <t>S-232</t>
         </is>
       </c>
       <c r="B40" s="3" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
@@ -1479,11 +1479,11 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>S-232</t>
+          <t>S-233</t>
         </is>
       </c>
       <c r="B41" s="3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
@@ -1504,11 +1504,11 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>S-233</t>
+          <t>S-234</t>
         </is>
       </c>
       <c r="B42" s="3" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
@@ -1529,11 +1529,11 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>S-234</t>
+          <t>S-235</t>
         </is>
       </c>
       <c r="B43" s="3" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
@@ -1554,11 +1554,11 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>S-235</t>
+          <t>S-236</t>
         </is>
       </c>
       <c r="B44" s="3" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
@@ -1579,11 +1579,11 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>S-236</t>
+          <t>S-237</t>
         </is>
       </c>
       <c r="B45" s="3" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>S-237</t>
+          <t>S-238</t>
         </is>
       </c>
       <c r="B46" s="3" t="n">
@@ -1629,11 +1629,11 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>S-238</t>
+          <t>S-338</t>
         </is>
       </c>
       <c r="B47" s="3" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
@@ -1654,11 +1654,11 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>S-338</t>
+          <t>Success Center</t>
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
@@ -1677,27 +1677,52 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Success Center</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>A,B,C,D,E,F,G</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>FY,S1,S2</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>I-111</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>30</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>FY,S1,S2</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>J-223</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>30</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>A,B,C,D,E,F,G</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>FY,S1,S2</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
